--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/setMemberActive-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/setMemberActive-bbt-form.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
   <si>
     <t>Statement: UserRepository.setMemberActive(memberId, isActive) – sets isActive flag.</t>
   </si>
@@ -139,7 +139,10 @@
     <t>memberId = ""</t>
   </si>
   <si>
-    <t>memberId = "a"</t>
+    <t>memberId = "a" (inex)</t>
+  </si>
+  <si>
+    <t>memberId = "a" (exist)</t>
   </si>
   <si>
     <t>BVA</t>
@@ -148,7 +151,19 @@
     <t>BVA-1 Empty</t>
   </si>
   <si>
-    <t>BVA-2 OneChar</t>
+    <t>BVA-2 InexChar</t>
+  </si>
+  <si>
+    <t>memberId = "a" (not in DB)</t>
+  </si>
+  <si>
+    <t>BVA-3 ExistChar</t>
+  </si>
+  <si>
+    <t>memberId = "a" (in DB)</t>
+  </si>
+  <si>
+    <t>Updates successfully</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -176,6 +191,12 @@
   </si>
   <si>
     <t>BVA-2</t>
+  </si>
+  <si>
+    <t>BVA-3</t>
+  </si>
+  <si>
+    <t>Success</t>
   </si>
   <si>
     <t>Testing</t>
@@ -905,7 +926,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C3"/>
+  <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -946,6 +967,17 @@
         <v>40</v>
       </c>
     </row>
+    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -954,7 +986,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -969,7 +1001,7 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C1" s="4" t="s">
         <v>23</v>
@@ -986,7 +1018,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>39</v>
@@ -1003,15 +1035,32 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>35</v>
       </c>
       <c r="E3" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1023,7 +1072,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1039,10 +1088,10 @@
         <v>21</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>23</v>
@@ -1065,10 +1114,10 @@
         <v>1</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>29</v>
@@ -1085,10 +1134,10 @@
         <v>1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="F3" s="5" t="s">
         <v>29</v>
@@ -1105,7 +1154,7 @@
         <v>1</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>35</v>
@@ -1122,7 +1171,7 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>39</v>
@@ -1142,7 +1191,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>40</v>
@@ -1151,6 +1200,26 @@
         <v>35</v>
       </c>
       <c r="F6" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="F7" s="5" t="s">
         <v>29</v>
       </c>
     </row>
@@ -1179,16 +1248,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>53</v>
+        <v>60</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1196,45 +1265,45 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>62</v>
+        <v>69</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>59</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>63</v>
+        <v>70</v>
       </c>
       <c r="B3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3" s="1">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1">
         <v>0</v>
@@ -1243,19 +1312,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
   </sheetData>

--- a/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/setMemberActive-bbt-form.xlsx
+++ b/Exam/gymtrackerpro/lib/repository/__tests__/bbt/user-repository/setMemberActive-bbt-form.xlsx
@@ -17,9 +17,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="74">
-  <si>
-    <t>Statement: UserRepository.setMemberActive(memberId, isActive) – sets isActive flag.</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="62">
+  <si>
+    <t>Statement: UserRepository.setMemberActive(id, isActive) – Sets the isActive flag on an existing member. Returns the updated MemberWithUser on success. Throws NotFoundError if no member exists with the given ID.</t>
   </si>
   <si>
     <t/>
@@ -31,25 +31,25 @@
     <t>Data</t>
   </si>
   <si>
-    <t>Input: memberId: string, isActive: boolean</t>
+    <t>Input: id: string, isActive: boolean</t>
   </si>
   <si>
     <t>precondition</t>
   </si>
   <si>
-    <t>Database is accessible</t>
+    <t>Database is accessible. A member with the given ID may or may not exist.</t>
   </si>
   <si>
     <t>Results</t>
   </si>
   <si>
-    <t>Output: Promise&lt;MemberWithUser&gt; | throws NotFoundError</t>
+    <t>Output: Promise&lt;MemberWithUser&gt;</t>
   </si>
   <si>
     <t>postcondition</t>
   </si>
   <si>
-    <t>isActive flag updated.</t>
+    <t>On success: MemberWithUser returned with result.isActive matching the input value. On failure: NotFoundError thrown.</t>
   </si>
   <si>
     <t>Number EC</t>
@@ -67,19 +67,13 @@
     <t>Member existence</t>
   </si>
   <si>
-    <t>Found</t>
-  </si>
-  <si>
-    <t>Not found (NotFoundError)</t>
-  </si>
-  <si>
-    <t>Active status</t>
-  </si>
-  <si>
-    <t>isActive = false</t>
-  </si>
-  <si>
-    <t>isActive = true</t>
+    <t>Existing ID, isActive: false → MemberWithUser returned with result.isActive: false</t>
+  </si>
+  <si>
+    <t>Existing ID, isActive: true → MemberWithUser returned with result.isActive: true</t>
+  </si>
+  <si>
+    <t>Non-existent ID → NotFoundError</t>
   </si>
   <si>
     <t>No TC</t>
@@ -97,34 +91,34 @@
     <t>Actual Result</t>
   </si>
   <si>
-    <t>EC-1, EC-3</t>
-  </si>
-  <si>
-    <t>id exists, isActive=false</t>
-  </si>
-  <si>
-    <t>Returns isActive=false</t>
+    <t>EC-1</t>
+  </si>
+  <si>
+    <t>id: MEMBER_ID, isActive: false</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.isActive: false</t>
   </si>
   <si>
     <t>Passed</t>
   </si>
   <si>
-    <t>EC-1, EC-4</t>
-  </si>
-  <si>
-    <t>id exists, isActive=true</t>
-  </si>
-  <si>
-    <t>Returns isActive=true</t>
-  </si>
-  <si>
     <t>EC-2</t>
   </si>
   <si>
-    <t>Non-existent member</t>
-  </si>
-  <si>
-    <t>Throws NotFoundError</t>
+    <t>id: MEMBER_ID, isActive: true</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.isActive: true</t>
+  </si>
+  <si>
+    <t>EC-3</t>
+  </si>
+  <si>
+    <t>id: NONEXISTENT_ID, isActive: true</t>
+  </si>
+  <si>
+    <t>throws NotFoundError</t>
   </si>
   <si>
     <t>Number BVA</t>
@@ -136,34 +130,28 @@
     <t>ID length</t>
   </si>
   <si>
-    <t>memberId = ""</t>
-  </si>
-  <si>
-    <t>memberId = "a" (inex)</t>
-  </si>
-  <si>
-    <t>memberId = "a" (exist)</t>
+    <t>0 chars (empty, not found), 1 char (not found), 1 char (found)</t>
   </si>
   <si>
     <t>BVA</t>
   </si>
   <si>
-    <t>BVA-1 Empty</t>
-  </si>
-  <si>
-    <t>BVA-2 InexChar</t>
-  </si>
-  <si>
-    <t>memberId = "a" (not in DB)</t>
-  </si>
-  <si>
-    <t>BVA-3 ExistChar</t>
-  </si>
-  <si>
-    <t>memberId = "a" (in DB)</t>
-  </si>
-  <si>
-    <t>Updates successfully</t>
+    <t>BVA-1 (n=0)</t>
+  </si>
+  <si>
+    <t>id: "", isActive: true</t>
+  </si>
+  <si>
+    <t>BVA-1 (n=1)</t>
+  </si>
+  <si>
+    <t>id: "a" (no match), isActive: true</t>
+  </si>
+  <si>
+    <t>id: "a" (found), isActive: true</t>
+  </si>
+  <si>
+    <t>MemberWithUser returned with result.id: "a"</t>
   </si>
   <si>
     <t>TC from EC</t>
@@ -172,33 +160,9 @@
     <t>TC from BVA</t>
   </si>
   <si>
-    <t>Exist, set inactive</t>
-  </si>
-  <si>
-    <t>isActive=false</t>
-  </si>
-  <si>
-    <t>Exist, set active</t>
-  </si>
-  <si>
-    <t>isActive=true</t>
-  </si>
-  <si>
-    <t>Non-existent ID</t>
-  </si>
-  <si>
     <t>BVA-1</t>
   </si>
   <si>
-    <t>BVA-2</t>
-  </si>
-  <si>
-    <t>BVA-3</t>
-  </si>
-  <si>
-    <t>Success</t>
-  </si>
-  <si>
     <t>Testing</t>
   </si>
   <si>
@@ -229,7 +193,7 @@
     <t>Re-tested</t>
   </si>
   <si>
-    <t>MEM-06</t>
+    <t>REPO-10</t>
   </si>
   <si>
     <t>n/a</t>
@@ -754,7 +718,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -795,13 +759,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>17</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -809,27 +773,13 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>18</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" ht="18" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="1">
-        <v>4</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -852,19 +802,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -872,16 +822,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="E2" s="5" t="s">
         <v>27</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="E2" s="5" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -889,16 +839,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>32</v>
-      </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -906,16 +856,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -926,7 +876,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:C2"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
@@ -936,13 +886,13 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
@@ -950,32 +900,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="1">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" ht="18" customHeight="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="1">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -998,19 +926,19 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="C1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1018,16 +946,16 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1035,16 +963,16 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -1052,16 +980,16 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1085,22 +1013,22 @@
   <sheetData>
     <row r="1" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D1" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B1" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="C1" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>23</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1108,19 +1036,19 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>52</v>
-      </c>
       <c r="F2" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1128,19 +1056,19 @@
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>54</v>
-      </c>
       <c r="F3" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1148,19 +1076,19 @@
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>35</v>
-      </c>
       <c r="F4" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1171,16 +1099,16 @@
         <v>1</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1191,16 +1119,16 @@
         <v>1</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -1211,16 +1139,16 @@
         <v>1</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>59</v>
+        <v>44</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>
@@ -1248,16 +1176,16 @@
         <v>1</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2"/>
       <c r="E1" s="2"/>
       <c r="F1" s="2" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
@@ -1265,39 +1193,39 @@
     </row>
     <row r="2" ht="25" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>63</v>
+        <v>51</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>67</v>
+        <v>55</v>
       </c>
       <c r="F2" s="4" t="s">
-        <v>68</v>
+        <v>56</v>
       </c>
       <c r="G2" s="4" t="s">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="H2" s="4" t="s">
-        <v>64</v>
+        <v>52</v>
       </c>
       <c r="I2" s="4" t="s">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="J2" s="4" t="s">
-        <v>66</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" ht="20" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>70</v>
+        <v>58</v>
       </c>
       <c r="B3" s="1">
         <v>6</v>
@@ -1312,19 +1240,19 @@
         <v>0</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>71</v>
+        <v>59</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>72</v>
+        <v>60</v>
       </c>
       <c r="H3" s="1">
         <v>0</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
     </row>
   </sheetData>
